--- a/data/digest_combined_2026-08-25.xlsx
+++ b/data/digest_combined_2026-08-25.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -603,22 +603,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Тайсон (TSN) Квартал у фокусі: Метрика доступних прибутків дає промах за звітний період; Акції впали на 1,04% за поточну сесію – основні моменти звіту про прибутки</t>
+          <t>Тайсон (TSN) Квартал у фокусі: Метрика доступних доходів забезпечує промах за звітний період; Акції впали на 1,04% за поточну сесію – основні моменти звіту про прибутки</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Тайсон (TSN) Квартал у фокусі: Метрика доступних прибутків дає промах за звітний період; Акції впали на 1,04% за поточну сесію – основні моменти звіту про прибутки</t>
+          <t>Тайсон (TSN) Квартал у фокусі: Метрика доступних доходів забезпечує промах за звітний період; Акції впали на 1,04% за поточну сесію – основні моменти звіту про прибутки</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Тайсон (TSN) Квартал у фокусі: Метрика доступних прибутків дає промах за звітний період; Акції впали на 1,04% за поточну сесію – огляд прибутків vinanet.vn</t>
+          <t>Тайсон (TSN) Квартал у фокусі: Метрика доступних доходів забезпечує промах за звітний період; Акції впали на 1,04% за поточну сесію – огляд прибутків vinanet.vn</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Тайсон (TSN) Квартал у фокусі: Метрика доступних прибутків дає промах за звітний період; Акції впали на 1,04% за поточну сесію – огляд прибутків vinanet.vn</t>
+          <t>Тайсон (TSN) Квартал у фокусі: Метрика доступних доходів забезпечує промах за звітний період; Акції впали на 1,04% за поточну сесію – огляд прибутків vinanet.vn</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Хоча хороші новини для заводу в Амарілло, реструктуризація Tyson є тривожним дзвінком для тваринницької промисловості Америки</t>
+          <t>Хоча хороші новини для заводу в Амарілло, реструктуризація Tyson є тривожним дзвінком для тваринницької галузі Америки</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Хоча хороші новини для заводу в Амарілло, реструктуризація Tyson є тривожним дзвінком для тваринницької промисловості Америки</t>
+          <t>Хоча хороші новини для заводу в Амарілло, реструктуризація Tyson є тривожним дзвінком для тваринницької галузі Америки</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1043,22 +1043,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Акції Tyson Foods залишаються стабільними, оскільки тендерна пропозиція змінює баланс - Ad-hoc-news.de</t>
+          <t>Акції Tyson Foods залишаються стабільними, оскільки тендерна пропозиція боргу змінює баланс - Ad-hoc-news.de</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Акції Tyson Foods залишаються стабільними, оскільки тендерна пропозиція змінює баланс - Ad-hoc-news.de</t>
+          <t>Акції Tyson Foods залишаються стабільними, оскільки тендерна пропозиція боргу змінює баланс - Ad-hoc-news.de</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Акції Tyson Foods залишаються стабільними, оскільки тендерна пропозиція боргу змінює баланс Ad-hoc-news.de</t>
+          <t>Акції Tyson Foods стабільні, оскільки тендерна пропозиція боргу змінює баланс Ad-hoc-news.de</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Акції Tyson Foods залишаються стабільними, оскільки тендерна пропозиція боргу змінює баланс Ad-hoc-news.de</t>
+          <t>Акції Tyson Foods стабільні, оскільки тендерна пропозиція боргу змінює баланс Ad-hoc-news.de</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Понад 3000 працівників звільнено через закриття м’ясокомбінатів Tyson Foods</t>
+          <t>Понад 3000 працівників звільнено, оскільки Tyson Foods закриває м’ясопереробні заводи</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Понад 3000 працівників звільнено через закриття м’ясокомбінатів Tyson Foods</t>
+          <t>Понад 3000 працівників звільнено, оскільки Tyson Foods закриває м’ясопереробні заводи</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1208,22 +1208,22 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Тайсон не очікує купівлі банкнот пізніше; Очікується, що вартість раннього тендеру перевищить максимальну суму в 1,2 мільярда доларів</t>
+          <t>Тайсон не очікує купівлі купюр пізніше; Очікується, що вартість раннього тендеру перевищить максимальну суму в 1,2 мільярда доларів</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Тайсон не очікує купівлі банкнот пізніше; Очікується, що вартість раннього тендеру перевищить максимальну суму в 1,2 мільярда доларів</t>
+          <t>Тайсон не очікує купівлі купюр пізніше; Очікується, що вартість раннього тендеру перевищить максимальну суму в 1,2 мільярда доларів</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Тайсон не очікує купівлі банкнот пізніше; Очікується, що витрати на ранніх тендерах перевищать максимальну суму Stock Titan у 1,2 мільярда доларів</t>
+          <t>Тайсон не очікує купівлі купюр пізніше; Очікується, що витрати на ранніх тендерах перевищать максимальну суму в $1,2 млрд. Stock Titan</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Тайсон не очікує купівлі банкнот пізніше; Очікується, що витрати на ранніх тендерах перевищать максимальну суму Stock Titan у 1,2 мільярда доларів</t>
+          <t>Тайсон не очікує купівлі купюр пізніше; Очікується, що витрати на ранніх тендерах перевищать максимальну суму в $1,2 млрд. Stock Titan</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>The Cool Down</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Закриття Tyson може збільшити витрати на яловичину, оскільки посуха в Техасі підштовхує стадо до мінімуму за 75 років Yahoo Finance</t>
+          <t>Закриття Tyson може збільшити витрати на яловичину, оскільки посуха в Техасі підштовхує стадо до мінімуму за 75 років The Cool Down</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Закриття Tyson може збільшити витрати на яловичину, оскільки посуха в Техасі підштовхує стадо до мінімуму за 75 років Yahoo Finance</t>
+          <t>Закриття Tyson може збільшити витрати на яловичину, оскільки посуха в Техасі підштовхує стадо до мінімуму за 75 років The Cool Down</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUk10ck5sazBRNHAyWnhVeG9zeTlERDFKQTFQVmUyemt6R0sxNEtUNGhUdmxrMjJfNUdBOTVYYzJRT2xzenpSN09xNWJxLVpQcWwxOEF0TENEZlZOUU1IRTNBekRNVUdycE9XQWNGdS1sQlVMWVdOUWhpZTNNaUNhY0cyZmI2ekJHTlhqMnZ0U2pmUTB1aWxsWUczZWs1cUVuQkh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNMmRrUDdZd0Fjd2FHdlZuQlBZTDMtazJuZFNrUExNakxQZGxaMVp1NkIyRVJXVGpZbFRNZ2FTLXkwdzV1ZHdjdlYwSmZMLVFSelJ1c3lDRkZwekVzUGJIdUkyczRXMkdYTTdFZVUzS1VHVWJCUTJYRUdxalk3UFp5enFWSXFoVFptc0E2cW9KWWVON00?oc=5</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Тайсон, JBS, щоб скоротити можливості різання</t>
+          <t>Тайсон, JBS, щоб скоротити можливості забою</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Тайсон, JBS, щоб скоротити можливості різання</t>
+          <t>Тайсон, JBS, щоб скоротити можливості забою</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Тайсон, JBS скоротять можливості забійної продукції The Fence Post</t>
+          <t>Тайсон, JBS скорочують можливості забійної продукції The Fence Post</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Тайсон, JBS скоротять можливості забійної продукції The Fence Post</t>
+          <t>Тайсон, JBS скорочують можливості забійної продукції The Fence Post</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1428,22 +1428,22 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Галузь великої рогатої худоби штату Айова поки що залишається стабільною, фермери хвилюються про майбутнє через закриття заводу Tyson</t>
+          <t>Галузь великої рогатої худоби штату Айова поки що залишається стабільною, фермери хвилюються за майбутнє через закриття заводу Tyson</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Галузь великої рогатої худоби штату Айова поки що залишається стабільною, фермери хвилюються про майбутнє через закриття заводу Tyson</t>
+          <t>Галузь великої рогатої худоби штату Айова поки що залишається стабільною, фермери хвилюються за майбутнє через закриття заводу Tyson</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Галузь великої рогатої худоби в штаті Айова поки що стабільна, фермери хвилюються про майбутнє через закриття заводу Tyson Dispatch Argus</t>
+          <t>Галузь великої рогатої худоби штату Айова поки що стабільна, фермери хвилюються про майбутнє через закриття заводу Tyson Dispatch Argus</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Галузь великої рогатої худоби в штаті Айова поки що стабільна, фермери хвилюються про майбутнє через закриття заводу Tyson Dispatch Argus</t>
+          <t>Галузь великої рогатої худоби штату Айова поки що стабільна, фермери хвилюються про майбутнє через закриття заводу Tyson Dispatch Argus</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Perdigão Na Brasa потрапляє в атмосферу Brasileirão з Мішелем Тело та дією на Globo</t>
+          <t>Perdigão Na Brasa потрапляє в атмосферу Brasileirão з Мішелем Тело та бойовиками на Globo</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Perdigão Na Brasa потрапляє в атмосферу Brasileirão з Мішелем Тело та дією на Globo</t>
+          <t>Perdigão Na Brasa потрапляє в атмосферу Brasileirão з Мішелем Тело та бойовиками на Globo</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>MBRF падає на 5% після оновлення оцінки JPMorgan, незважаючи на зростання цін</t>
+          <t>MBRF падає на 5% після оновлення оцінки JPMorgan, незважаючи на підвищення ціни</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>MBRF падає на 5% після оновлення оцінки JPMorgan, незважаючи на зростання цін</t>
+          <t>MBRF падає на 5% після оновлення оцінки JPMorgan, незважаючи на підвищення ціни</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Прибуток MBRF (MBRF3) впав на 92% у 4 кварталі 25 р. до 91 мільйона реалів</t>
+          <t>Прибуток MBRF (MBRF3) різко впав на 92% у 4 кварталі 25 р. до 91 мільйона реалів</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Прибуток MBRF (MBRF3) впав на 92% у 4 кварталі 25 р. до 91 мільйона реалів</t>
+          <t>Прибуток MBRF (MBRF3) різко впав на 92% у 4 кварталі 25 р. до 91 мільйона реалів</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Радник просить дослідження зв’язку між Rua Catarina Mafessoni та MBRF у Concórdia</t>
+          <t>Радник просить дослідження зв’язку між Rua Catarina Mafessoni та MBRF, у Concórdia</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Радник просить дослідження зв’язку між Rua Catarina Mafessoni та MBRF у Concórdia</t>
+          <t>Радник просить дослідження зв’язку між Rua Catarina Mafessoni та MBRF, у Concórdia</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2023,32 +2023,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23 18:32:21</t>
+          <t>2026-08-23 23:00:00</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Seu Dinheiro</t>
+          <t>Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Хочеш перемогти Ібовеспу? Цього тижня Terra робить ставки на WEG (WEGE3), MBRF (MBRF3) та ще 3 акції</t>
+          <t>Minerva, JBS і MBRF: хто більше виграє від призупинення тарифу на яловичину в США</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Хочеш перемогти Ібовеспу? Цього тижня Terra робить ставки на WEG (WEGE3), MBRF (MBRF3) та ще 3 акції</t>
+          <t>Minerva, JBS і MBRF: хто більше виграє від призупинення тарифу на яловичину в США</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Хочеш перемогти Ібовеспу? Terra робить ставки на WEG (WEGE3), MBRF (MBRF3) і ще 3 акції цього тижня Ваші гроші</t>
+          <t>Minerva, JBS і MBRF: хто може більше виграти від призупинення тарифу на яловичину в США Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Хочеш перемогти Ібовеспу? Terra робить ставки на WEG (WEGE3), MBRF (MBRF3) і ще 3 акції цього тижня Ваші гроші</t>
+          <t>Minerva, JBS і MBRF: хто може більше виграти від призупинення тарифу на яловичину в США Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2061,7 +2061,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQY2d2dVR4dm4yc1hITzVrOU5NNUtFZG9vbjlMOGlZb2lDcDlONzc2djBIRUcyZE9QY0pRRVZLRFBrQ2tLWGVaMlV1RFdEbDhzcXRNRk9LNVlpZFl0N1FrV2JfVnNxQTljUUVvVmxVcldicUUwU0RIcnpSb0czajc0bUMwbjlUd2hpTnFXVWtSX1V0XzE1WVVIUmlDY3RXN2dfMG9qV2ZnVUFlZTVwc2dKQmxHVC1OS1lpZlhrVWZZQkh5bTFyNXlFNEgzYlBEaXo1ekFLZjJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPbnk3UTI2M0ZySnpzaTBWOHR6bmZ5bGlKVElYaTlGTWRqcWQ5b2s2VEZEVzhqLVI1QVFIWWphb2dRTDljQ2tGWWJ4Q1JzNjI1Zmc1UUs3N3R5d29QODlCU2g0U1ZjbGtIRUZPQ3N2UGZ6Yk1KZ0hOZ19sSV9HcFp0Z1lYM0ZBNjI0b2dXcmE5Wm5MSU5HRW9SWmc2Q1FKLVhvSUNfNWlhRmJiQ29uRXhfenV2bHZPRkNOdHBiMTVlWjZGdk5JUk9DT1hXTzJQeklz?oc=5</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2078,37 +2078,37 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 17:56:56</t>
+          <t>2026-08-23 18:32:21</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Finimize</t>
+          <t>Seu Dinheiro</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>UBS бачить більш чітку злітну смугу для JBS до 2028 року</t>
+          <t>Хочеш перемогти Ібовеспу? Terra робить ставки на WEG (WEGE3), MBRF (MBRF3) і ще 3 акції цього тижня</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>UBS бачить більш чітку злітну смугу для JBS до 2028 року</t>
+          <t>Хочеш перемогти Ібовеспу? Terra робить ставки на WEG (WEGE3), MBRF (MBRF3) і ще 3 акції цього тижня</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>UBS бачить більш чітку злітну смугу для JBS до 2028 Finimize</t>
+          <t>Хочеш перемогти Ібовеспу? Terra робить ставки на WEG (WEGE3), MBRF (MBRF3) і ще 3 акції цього тижня Ваші гроші</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>UBS бачить більш чітку злітну смугу для JBS до 2028 Finimize</t>
+          <t>Хочеш перемогти Ібовеспу? Terra робить ставки на WEG (WEGE3), MBRF (MBRF3) і ще 3 акції цього тижня Ваші гроші</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>JBS</t>
+          <t>BRF</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2116,12 +2116,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1HajJ4X05WQ2Y3YzlWWnVPV3hQaWNXSDhlRE5GNmpGMENOTU9GeWhFaFI0WjE0ejFRX19jRDlxamtmMnRaU1BPRGczdDdBcFZlTktxaEUxdnBWT0FGX1B0ZEIyelNtdjVCdFlKM2szMUd2MVB6MFlTVE1XamU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQY2d2dVR4dm4yc1hITzVrOU5NNUtFZG9vbjlMOGlZb2lDcDlONzc2djBIRUcyZE9QY0pRRVZLRFBrQ2tLWGVaMlV1RFdEbDhzcXRNRk9LNVlpZFl0N1FrV2JfVnNxQTljUUVvVmxVcldicUUwU0RIcnpSb0czajc0bUMwbjlUd2hpTnFXVWtSX1V0XzE1WVVIUmlDY3RXN2dfMG9qV2ZnVUFlZTVwc2dKQmxHVC1OS1lpZlhrVWZZQkh5bTFyNXlFNEgzYlBEaXo1ekFLZjJn?oc=5</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>competitor_jbs_2026-08-25.csv</t>
+          <t>competitor_brf_2026-08-25.csv</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:26:47</t>
+          <t>2026-08-24 17:56:56</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>JBS Foods</t>
+          <t>Finimize</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>JBS Australia робить внесок у «Flanno for a Farmer Day» від Farm Angels</t>
+          <t>UBS бачить більш чітку злітну смугу для JBS до 2028 року</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>JBS Australia робить внесок у «Flanno for a Farmer Day» від Farm Angels</t>
+          <t>UBS бачить більш чітку злітну смугу для JBS до 2028 року</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>JBS Australia робить внесок у «Flanno for a Farmer Day» від Farm Angels JBS Foods</t>
+          <t>UBS бачить більш чітку злітну смугу для JBS до 2028 Finimize</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>JBS Australia робить внесок у «Flanno for a Farmer Day» від Farm Angels JBS Foods</t>
+          <t>UBS бачить більш чітку злітну смугу для JBS до 2028 Finimize</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMGFaT1JGWWtJRFlVc3RuV2lTMFhfRzIwVzcwZVQ2cXVnR2xEVHlLTEVXTUdGLUlCQm9IVmt0RmdSdW9qMTQ5aUlnVEdISFIyZ1NBQjJMX1B1OFdTb3M3LUdJN0EwWWZKT1RMb3FrblZIMDZRYTBuUHFOYzRpN0RtMUpVLXVUSmdMQlpnMGxmWWc4cmN2NmJ2SjVGYTFHZ0N1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1HajJ4X05WQ2Y3YzlWWnVPV3hQaWNXSDhlRE5GNmpGMENOTU9GeWhFaFI0WjE0ejFRX19jRDlxamtmMnRaU1BPRGczdDdBcFZlTktxaEUxdnBWT0FGX1B0ZEIyelNtdjVCdFlKM2szMUd2MVB6MFlTVE1XamU?oc=5</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2188,32 +2188,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 08:03:19</t>
+          <t>2026-08-24 16:26:47</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Valor Econômico</t>
+          <t>JBS Foods</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Брати Батіста, власники JBS, купують оборонну компанію Avibras</t>
+          <t>JBS Australia робить внесок у «Flanno for a Farmer Day» від Farm Angels</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Брати Батіста, власники JBS, купують оборонну компанію Avibras</t>
+          <t>JBS Australia робить внесок у «Flanno for a Farmer Day» від Farm Angels</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Брати Батіста, власники JBS, купують оборонну компанію Avibras Valor Econômico</t>
+          <t>JBS Australia робить внесок у «Flanno for a Farmer Day» JBS Foods від Farm Angels</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Брати Батіста, власники JBS, купують оборонну компанію Avibras Valor Econômico</t>
+          <t>JBS Australia робить внесок у «Flanno for a Farmer Day» JBS Foods від Farm Angels</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUnRnV0d6QWNJenUxUUFvWUNlOFViUG9QeG5Wb1cxNDBhcnJNcmlZd0ZvbFRnNHotWERZOEhUWm5kdV9ydE9NWHh5UDdlcUdaMk9Cam56OE5WbG9jZ1ZPRHZPUDR1bWJVYWNac0trSF81OUQ0cDVZUzcxcXdJX1Fwb0lMNnR2Vl81Y0VnNUppYUlCeGpIeVp3NkNfVWRHRmFuWENKWWstRlZZOUM3NXRzR3dBdW5fSUxiMll30gHKAUFVX3lxTE1uLWdwTUFmeFVkUlQzZ0tKeGdyVW1xVkw3UldjOWVwcWJZQVpZMWR5TEtBY3ByVUtmNUFWdDY5d2M5TGtfZlVOVjI0alIxLUVFaDNaVmJPanYyNEhldzRWN05xdGtnQ3VIRktWNWZ4LXZMOThpWkdLZkFMWTNteHJkel9JYXY3eWFUZndZX2ZnTkhFWWVIOFM3aWRpaDBnb1hxN1lxZXlvTGxxb0F2MTF2YlRvYlJhemNBV0FCd3Z6LVBsaEFoT3NBa0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMGFaT1JGWWtJRFlVc3RuV2lTMFhfRzIwVzcwZVQ2cXVnR2xEVHlLTEVXTUdGLUlCQm9IVmt0RmdSdW9qMTQ5aUlnVEdISFIyZ1NBQjJMX1B1OFdTb3M3LUdJN0EwWWZKT1RMb3FrblZIMDZRYTBuUHFOYzRpN0RtMUpVLXVUSmdMQlpnMGxmWWc4cmN2NmJ2SjVGYTFHZ0N1?oc=5</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2243,32 +2243,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 00:34:31</t>
+          <t>2026-08-24 08:03:19</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nord Investimentos</t>
+          <t>Valor Econômico</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>JBS (JBSS32) має на +15% більший прибуток у 2025 році</t>
+          <t>Брати Батіста, власники JBS, купують оборонну компанію Avibras</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>JBS (JBSS32) має на +15% більший прибуток у 2025 році</t>
+          <t>Брати Батіста, власники JBS, купують оборонну компанію Avibras</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>JBS (JBSS32) має на 15% більший прибуток у 2025 Nord Investimentos</t>
+          <t>Брати Батіста, власники JBS, купують оборонну компанію Avibras Valor Econômico</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>JBS (JBSS32) має на 15% більший прибуток у 2025 Nord Investimentos</t>
+          <t>Брати Батіста, власники JBS, купують оборонну компанію Avibras Valor Econômico</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9qeEpZSnZMZUZ4bUpCYWFGSkxCUWZ0UkFsWXU5WHBfQTk0RmhOV0FzeHRFV09TS2ZuRnMtbmR3S1FNSHJVNVhiU3NXVXNiNEpRV2xMYjdoNEVzLUN5VWpvM2szdlBZVC1vOXB5N1R4enF3LTUzQjFDddIBfkFVX3lxTE5Dd3UxcnVaZUhrY09RYVN4Z1MtWHQzbVd6Sy05d3JueTdNWnlObmFIT0JScURkS3lMa0l2MUpCanRWYUdQdFN1emJYaXJLTXRWN002RThZS0ZjT2pDZEwwX0EtQkdEV2F5TEZKejF5MDBYVTNpRkZuVmkxZThGQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUnRnV0d6QWNJenUxUUFvWUNlOFViUG9QeG5Wb1cxNDBhcnJNcmlZd0ZvbFRnNHotWERZOEhUWm5kdV9ydE9NWHh5UDdlcUdaMk9Cam56OE5WbG9jZ1ZPRHZPUDR1bWJVYWNac0trSF81OUQ0cDVZUzcxcXdJX1Fwb0lMNnR2Vl81Y0VnNUppYUlCeGpIeVp3NkNfVWRHRmFuWENKWWstRlZZOUM3NXRzR3dBdW5fSUxiMll30gHKAUFVX3lxTE1uLWdwTUFmeFVkUlQzZ0tKeGdyVW1xVkw3UldjOWVwcWJZQVpZMWR5TEtBY3ByVUtmNUFWdDY5d2M5TGtfZlVOVjI0alIxLUVFaDNaVmJPanYyNEhldzRWN05xdGtnQ3VIRktWNWZ4LXZMOThpWkdLZkFMWTNteHJkel9JYXY3eWFUZndZX2ZnTkhFWWVIOFM3aWRpaDBnb1hxN1lxZXlvTGxxb0F2MTF2YlRvYlJhemNBV0FCd3Z6LVBsaEFoT3NBa0E?oc=5</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2298,32 +2298,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 23:36:13</t>
+          <t>2026-08-24 00:34:31</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Jornal O Sul</t>
+          <t>Nord Investimentos</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Брати Джослі та Уеслі Батіста, власники Friboi, купили Avibras, найбільшу збройову промисловість у країні, яка має контракти з армією та бразильськими ВПС</t>
+          <t>JBS (JBSS32) має на +15% більший прибуток у 2025 році</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Брати Джослі та Уеслі Батіста, власники Friboi, купили Avibras, найбільшу збройову промисловість у країні, яка має контракти з армією та бразильськими ВПС</t>
+          <t>JBS (JBSS32) має на +15% більший прибуток у 2025 році</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Брати Джослі та Веслі Батіста, власники Friboi, купили Avibras, найбільшу збройову промисловість у країні, яка підтримує контракти з армією та бразильськими ВПС Jornal O Sul</t>
+          <t>JBS (JBSS32) має на 15% більший прибуток у 2025 Nord Investimentos</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Брати Джослі та Веслі Батіста, власники Friboi, купили Avibras, найбільшу збройову промисловість у країні, яка підтримує контракти з армією та бразильськими ВПС Jornal O Sul</t>
+          <t>JBS (JBSS32) має на 15% більший прибуток у 2025 Nord Investimentos</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxNYXpTeW1CVE5SeDdDX24xTmo4VkVCVmE0WlNTY2hqajZlSE8xV0xhbU81SFhtNlJIOXB6dTI0eEtsTlNmbUtrbXVKQlYySzBRNjRiR1NNRkpYaHlfd1ltSHZrMGpHc25aVG95anRfeVpGaHpPSWItei1ZODdkUlFSN0xKd3lGNmFLWmwxbHV4bnVTQU9KUEpfREF2eUxUUDJtWC1MbVYyUnFBUnJwR0xLVEdTTUlseEIxZ205WjRQVmZPZU05VG9xSlVNNzhsa25kZ2xSUWczNW44Qi1UOEdXSG1pWm9nQXozV3BDQTNxcGNjNHRzRW1pY1ZKcjRTd3FZNV93TUZpVHZkVG1zNFJwSlk2MVI4aTZPUDdEakhCWEjSAaYCQVVfeXFMTTlrVzhsWk4yUXRsZXlJbjhaelBVLVc1NDJrTFhXNG5nVUdQUHJSWWgtYjgtV3ZtTUhqZjA0OWNBM0tBY2hkcm9TclBwYUpfQXcwckZGVzFxV2ozM0pjS3FWYnhEdGF3QzdZa2UzckxibzUxOVdPR3lQdFlJZnp2NmZLTDdJQjRVb3FaWEJQTHFMTUtBSVhycU1VcER6MkpLREowcEpBUjBhNmtydldHdVZtYWpkNjRHb0YzU1FIaWw5aUo5R2luX3ktLXBhbEJYaUxMZHlNcGdVX2xGOXFsbjZVVlpOQ19jV2tKT2JGTkhzdlNJcFFoSTVNaE5WSWRPajRNLWlqbHpPZEsxUGh5YkNoVUljcF9xMkMwQy1JZGhNWUNUS1NB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9qeEpZSnZMZUZ4bUpCYWFGSkxCUWZ0UkFsWXU5WHBfQTk0RmhOV0FzeHRFV09TS2ZuRnMtbmR3S1FNSHJVNVhiU3NXVXNiNEpRV2xMYjdoNEVzLUN5VWpvM2szdlBZVC1vOXB5N1R4enF3LTUzQjFDddIBfkFVX3lxTE5Dd3UxcnVaZUhrY09RYVN4Z1MtWHQzbVd6Sy05d3JueTdNWnlObmFIT0JScURkS3lMa0l2MUpCanRWYUdQdFN1emJYaXJLTXRWN002RThZS0ZjT2pDZEwwX0EtQkdEV2F5TEZKejF5MDBYVTNpRkZuVmkxZThGQQ?oc=5</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2353,32 +2353,32 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 22:13:47</t>
+          <t>2026-08-22 23:36:13</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Notícias Agrícolas</t>
+          <t>Jornal O Sul</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>В’єтнам дозволяє ще двом бразильським бійням JBS експортувати яловичину</t>
+          <t>Брати Джослі та Уеслі Батіста, власники Friboi, купили Avibras, найбільшу збройову промисловість у країні, яка має контракти з армією та бразильськими ВПС</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>В’єтнам дозволяє ще двом бразильським бійням JBS експортувати яловичину</t>
+          <t>Брати Джослі та Уеслі Батіста, власники Friboi, купили Avibras, найбільшу збройову промисловість у країні, яка має контракти з армією та бразильськими ВПС</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>В’єтнам дає змогу ще двом бразильським бійням JBS експортувати яловичину Новини сільського господарства</t>
+          <t>Брати Джослі та Уеслі Батіста, власники Friboi, купили Avibras, найбільшу збройову промисловість у країні, яка підтримує контракти з армією та бразильськими ВПС Jornal O Sul</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>В’єтнам дає змогу ще двом бразильським бійням JBS експортувати яловичину Новини сільського господарства</t>
+          <t>Брати Джослі та Уеслі Батіста, власники Friboi, купили Avibras, найбільшу збройову промисловість у країні, яка підтримує контракти з армією та бразильськими ВПС Jornal O Sul</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxORjBEV1Y2LWNjN2JDYlBub3ljSE9RT0p1Zk9kOXpfUVlNeXJUU3lEVkV3aUJwemNBclR3a2Vpd1oxbmc1VVVLYkZ4b1Jaa2dqRi1vOXBETE81aDJnUG9JdlFsUm1ueFliMjV3eUNYWG5FM2lMLVF1cFhlOHZXTGtBQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxNYXpTeW1CVE5SeDdDX24xTmo4VkVCVmE0WlNTY2hqajZlSE8xV0xhbU81SFhtNlJIOXB6dTI0eEtsTlNmbUtrbXVKQlYySzBRNjRiR1NNRkpYaHlfd1ltSHZrMGpHc25aVG95anRfeVpGaHpPSWItei1ZODdkUlFSN0xKd3lGNmFLWmwxbHV4bnVTQU9KUEpfREF2eUxUUDJtWC1MbVYyUnFBUnJwR0xLVEdTTUlseEIxZ205WjRQVmZPZU05VG9xSlVNNzhsa25kZ2xSUWczNW44Qi1UOEdXSG1pWm9nQXozV3BDQTNxcGNjNHRzRW1pY1ZKcjRTd3FZNV93TUZpVHZkVG1zNFJwSlk2MVI4aTZPUDdEakhCWEjSAaYCQVVfeXFMTTlrVzhsWk4yUXRsZXlJbjhaelBVLVc1NDJrTFhXNG5nVUdQUHJSWWgtYjgtV3ZtTUhqZjA0OWNBM0tBY2hkcm9TclBwYUpfQXcwckZGVzFxV2ozM0pjS3FWYnhEdGF3QzdZa2UzckxibzUxOVdPR3lQdFlJZnp2NmZLTDdJQjRVb3FaWEJQTHFMTUtBSVhycU1VcER6MkpLREowcEpBUjBhNmtydldHdVZtYWpkNjRHb0YzU1FIaWw5aUo5R2luX3ktLXBhbEJYaUxMZHlNcGdVX2xGOXFsbjZVVlpOQ19jV2tKT2JGTkhzdlNJcFFoSTVNaE5WSWRPajRNLWlqbHpPZEsxUGh5YkNoVUljcF9xMkMwQy1JZGhNWUNUS1NB?oc=5</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2408,32 +2408,32 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 21:19:14</t>
+          <t>2026-08-22 22:13:47</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>Notícias Agrícolas</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Газета Мідіамакс. . Суд зробив ще один крок у позові проти JBS за неприємний запах із холодильної установки в районі Нова-Кампо-Гранде та регіоні столиці. Цього тижня суддя Едуардо Ласерда Тревізан з 2-го Суду з розсіяних прав, колективний</t>
+          <t>В’єтнам дозволяє ще двом бразильським бійням JBS експортувати яловичину</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Газета Мідіамакс. . Суд зробив ще один крок у позові проти JBS за неприємний запах із холодильної установки в районі Нова-Кампо-Гранде та регіоні столиці. Цього тижня суддя Едуардо Ласерда Тревізан з 2-го Суду з розсіяних прав, колективний</t>
+          <t>В’єтнам дозволяє ще двом бразильським бійням JBS експортувати яловичину</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Газета Мідіамакс. . Суд зробив ще один крок у позові проти JBS за неприємний запах із холодильної установки в районі Нова-Кампо-Гранде та регіоні столиці. Цього тижня суддя Едуардо Ласерда Тревізан з 2-го суду з розсіяних прав, Coletivo facebook.com</t>
+          <t>В’єтнам дає змогу ще двом бразильським бійням JBS експортувати яловичину Новини сільського господарства</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Газета Мідіамакс. . Суд зробив ще один крок у позові проти JBS за неприємний запах із холодильної установки в районі Нова-Кампо-Гранде та регіоні столиці. Цього тижня суддя Едуардо Ласерда Тревізан з 2-го суду з розсіяних прав, Coletivo facebook.com</t>
+          <t>В’єтнам дає змогу ще двом бразильським бійням JBS експортувати яловичину Новини сільського господарства</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPNlNZWDNZVDlBTFBLeEFNR0tOektwUEI2eHF3c2JTS0tTb1R5OE5LUHIyT2t3QWdETjB3Tl82OE8wM2VyX3Uxak81bDJfOEpVMTI0M1J2VkFnZGZkdEdrX21hNFdtUmNMdm5WMUlaTlRIeEVDQ2tRWUZXYjRYOHlhYUVWbEJXRXpCakVEc2oxWG9NTmpwT2otQmxJLTZSbGx0bG04NkpkV0pMYjNvZ1RCZ280aExsVXhJTDVCZi14RDlJMFNvRWpKano2Sl9QZ242RnZtQ3JQNWpQUXRfb0Rwa01lVGRYVG1iOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxORjBEV1Y2LWNjN2JDYlBub3ljSE9RT0p1Zk9kOXpfUVlNeXJUU3lEVkV3aUJwemNBclR3a2Vpd1oxbmc1VVVLYkZ4b1Jaa2dqRi1vOXBETE81aDJnUG9JdlFsUm1ueFliMjV3eUNYWG5FM2lMLVF1cFhlOHZXTGtBQw?oc=5</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 21:11:00</t>
+          <t>2026-08-22 21:19:14</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CompreRural</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>У віці 66 років власник Friboi почав працювати у віці 14 років верхи на ослі, а сьогодні заробляє 8 мільярдів реалів на своїй м’ясній імперії</t>
+          <t>Газета Мідіамакс. . Суд зробив ще один крок у позові проти JBS за неприємний запах із холодильної установки в районі Нова-Кампо-Гранде та регіоні столиці. Цього тижня суддя Едуардо Ласерда Тревізан з 2-го Суду з розсіяних прав, колективний</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>У віці 66 років власник Friboi почав працювати у віці 14 років верхи на ослі, а сьогодні заробляє 8 мільярдів реалів на своїй м’ясній імперії</t>
+          <t>Газета Мідіамакс. . Суд зробив ще один крок у позові проти JBS за неприємний запах із холодильної установки в районі Нова-Кампо-Гранде та регіоні столиці. Цього тижня суддя Едуардо Ласерда Тревізан з 2-го Суду з розсіяних прав, колективний</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>У віці 66 років власник Friboi почав працювати у віці 14 років, їздячи верхи на ослі, і сьогодні заробляє 8 мільярдів реалів на своїй м’ясній імперії CompreRural.</t>
+          <t>Газета Мідіамакс. . Суд зробив ще один крок у позові проти JBS за неприємний запах із холодильної установки в районі Нова-Кампо-Гранде та регіоні столиці. Цього тижня суддя Едуардо Ласерда Тревізан з 2-го суду з дифузних прав, Coletivo facebook.com</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>У віці 66 років власник Friboi почав працювати у віці 14 років, їздячи верхи на ослі, і сьогодні заробляє 8 мільярдів реалів на своїй м’ясній імперії CompreRural.</t>
+          <t>Газета Мідіамакс. . Суд зробив ще один крок у позові проти JBS за неприємний запах із холодильної установки в районі Нова-Кампо-Гранде та регіоні столиці. Цього тижня суддя Едуардо Ласерда Тревізан з 2-го суду з дифузних прав, Coletivo facebook.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPMWZMU0t1UG1tWkdFOVZNSDcxWUs4di1MX0pqa3I0Q0JvU01mRkhQNTN1RGJyY1hkQUE1TEtwSWtsVDhNbkdrMURMZ3JIYVdKYnQ3VXFyejFTOERQSTBqR2taQmxlbGhBMzVYU3diaWM0U0NzMFByTjVCbmExTWFaOWlhSm1BcEVwTGpzRnY0MzdoZk9TSlNpd29VR1EzVWxCVGN3YlZxNnU4d0FoVXF1LUZ1M2FHUU9XRmpNSzI2RVNWMS1nSWhWUHpkUkN5Q3lIbWlvckhkaFpXZDRITEhRQlVkV0VDZEh1enVWcEc2UzlxVk40Qk9tbU5BWHBfa0N5ZF9EQXVrUnRJYnNQYTZjMFBKcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPNlNZWDNZVDlBTFBLeEFNR0tOektwUEI2eHF3c2JTS0tTb1R5OE5LUHIyT2t3QWdETjB3Tl82OE8wM2VyX3Uxak81bDJfOEpVMTI0M1J2VkFnZGZkdEdrX21hNFdtUmNMdm5WMUlaTlRIeEVDQ2tRWUZXYjRYOHlhYUVWbEJXRXpCakVEc2oxWG9NTmpwT2otQmxJLTZSbGx0bG04NkpkV0pMYjNvZ1RCZ280aExsVXhJTDVCZi14RDlJMFNvRWpKano2Sl9QZ242RnZtQ3JQNWpQUXRfb0Rwa01lVGRYVG1iOGc?oc=5</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2518,32 +2518,32 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 12:11:32</t>
+          <t>2026-08-22 21:11:00</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Money Times</t>
+          <t>CompreRural</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Власники JBS купують Avibras і заходять в оборонний сектор; трансакція залежить від цього фактора</t>
+          <t>У віці 66 років власник Friboi почав працювати у віці 14 років, їздячи верхи на ослі, і сьогодні заробляє 8 мільярдів реалів на своїй м’ясній імперії</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Власники JBS купують Avibras і заходять в оборонний сектор; трансакція залежить від цього фактора</t>
+          <t>У віці 66 років власник Friboi почав працювати у віці 14 років, їздячи верхи на ослі, і сьогодні заробляє 8 мільярдів реалів на своїй м’ясній імперії</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Власники JBS купують Avibras і заходять в оборонний сектор; транзакція залежить від цього фактора. Money Times</t>
+          <t>У віці 66 років власник Friboi почав працювати у віці 14 років, їздячи верхи на ослі, і сьогодні заробляє 8 мільярдів реалів на своїй м’ясній імперії CompreRural.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Власники JBS купують Avibras і заходять в оборонний сектор; транзакція залежить від цього фактора. Money Times</t>
+          <t>У віці 66 років власник Friboi почав працювати у віці 14 років, їздячи верхи на ослі, і сьогодні заробляє 8 мільярдів реалів на своїй м’ясній імперії CompreRural.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNVjdyMjB2b1pNdldicGhaSm9qWG1ESVEtLVk2QzBOOE8tVGN2OTg4dFMyYXlRU2ozNjJnb3RwbnBkbGVCY25RMlhSY3gzekg0TVVvSGdtZkU4VEVJdkJBVjByN2c5ZDEyX3BpanR6aEtabGhocGNvNE5laHpPam9VdnlnV1hJeFlhMWNzUGt4VjJZaFVfNkNqZ05XRVVSc29zMDBaWERGWldHZ3lUYXk1Q1RaYVZyTlJrb3lxT0UwRzZZSEpKMmJ3VWRKMjNjUWhvS1Nz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPMWZMU0t1UG1tWkdFOVZNSDcxWUs4di1MX0pqa3I0Q0JvU01mRkhQNTN1RGJyY1hkQUE1TEtwSWtsVDhNbkdrMURMZ3JIYVdKYnQ3VXFyejFTOERQSTBqR2taQmxlbGhBMzVYU3diaWM0U0NzMFByTjVCbmExTWFaOWlhSm1BcEVwTGpzRnY0MzdoZk9TSlNpd29VR1EzVWxCVGN3YlZxNnU4d0FoVXF1LUZ1M2FHUU9XRmpNSzI2RVNWMS1nSWhWUHpkUkN5Q3lIbWlvckhkaFpXZDRITEhRQlVkV0VDZEh1enVWcEc2UzlxVk40Qk9tbU5BWHBfa0N5ZF9EQXVrUnRJYnNQYTZjMFBKcw?oc=5</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2573,32 +2573,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:39:00</t>
+          <t>2026-08-22 12:11:32</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Midiamax</t>
+          <t>Money Times</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Справа проти JBS за неприємний запах ставить холодильник на лаву підсудних</t>
+          <t>Власники JBS купують Avibras і заходять в оборонний сектор; транзакція залежить від цього фактора</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Справа проти JBS за неприємний запах ставить холодильник на лаву підсудних</t>
+          <t>Власники JBS купують Avibras і заходять в оборонний сектор; транзакція залежить від цього фактора</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Справа проти JBS через неприємний запах ставить холодильник «на лаву підсудних» Midiamax</t>
+          <t>Власники JBS купують Avibras і заходять в оборонний сектор; транзакція залежить від цього фактора. Money Times</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Справа проти JBS через неприємний запах ставить холодильник «на лаву підсудних» Midiamax</t>
+          <t>Власники JBS купують Avibras і заходять в оборонний сектор; транзакція залежить від цього фактора. Money Times</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2611,10 +2611,65 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNVjdyMjB2b1pNdldicGhaSm9qWG1ESVEtLVk2QzBOOE8tVGN2OTg4dFMyYXlRU2ozNjJnb3RwbnBkbGVCY25RMlhSY3gzekg0TVVvSGdtZkU4VEVJdkJBVjByN2c5ZDEyX3BpanR6aEtabGhocGNvNE5laHpPam9VdnlnV1hJeFlhMWNzUGt4VjJZaFVfNkNqZ05XRVVSc29zMDBaWERGWldHZ3lUYXk1Q1RaYVZyTlJrb3lxT0UwRzZZSEpKMmJ3VWRKMjNjUWhvS1Nz?oc=5</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>competitor_jbs_2026-08-25.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 10:39:00</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Midiamax</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Справа проти JBS через неприємний запах ставить холодильник на лаву підсудних</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Справа проти JBS через неприємний запах ставить холодильник на лаву підсудних</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Справа проти JBS через неприємний запах ставить холодильник «на лаву підсудних» Midiamax</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Справа проти JBS через неприємний запах ставить холодильник «на лаву підсудних» Midiamax</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>JBS</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPME01dFVqWUtSR0RCRlk5N0xObVN4ZUNVdWQwcWJ4cGtnUlVTd0dTNF80ekhsOEtFRk9pNFNkcEV6YW1NS2VDdE9pR2hramMwYWl4YmZsTjVWbG5XZWVCQ2xUVlNpdEx5STdKZ2RXbzEySlhSLVFGUmpMekRuTXAyRG1NWXBjaHpIdW9CTkRJa0dxczJTMC02T2s1LVEwTWI2a1ZEeTdnR3A3SUNzOEVHdTl4X3dwWkVxN3RBZGJ5Y1JXR0RjMWh5R2lJaUxaUQ?oc=5</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>competitor_jbs_2026-08-25.csv</t>
         </is>
@@ -2661,6 +2716,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
